--- a/public/uploads/files/sample_filter.xlsx
+++ b/public/uploads/files/sample_filter.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7290"/>
+    <workbookView windowWidth="19200" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>filtergroup_name</t>
   </si>
@@ -38,7 +38,7 @@
     <t>category</t>
   </si>
   <si>
-    <t xml:space="preserve">Active </t>
+    <t>Active</t>
   </si>
   <si>
     <t>Ton</t>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>capactiy</t>
-  </si>
-  <si>
-    <t>Active</t>
   </si>
   <si>
     <t>connectivity</t>
@@ -1257,12 +1254,12 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>

--- a/public/uploads/files/sample_filter.xlsx
+++ b/public/uploads/files/sample_filter.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>filtergroup_name</t>
   </si>
@@ -35,22 +35,19 @@
     <t>status</t>
   </si>
   <si>
-    <t>category</t>
+    <t>Category</t>
   </si>
   <si>
     <t>Active</t>
   </si>
   <si>
-    <t>Ton</t>
+    <t>Connectivity</t>
   </si>
   <si>
     <t>Inactive</t>
   </si>
   <si>
-    <t>capactiy</t>
-  </si>
-  <si>
-    <t>connectivity</t>
+    <t>No of Ports</t>
   </si>
 </sst>
 </file>
@@ -1218,8 +1215,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="4" outlineLevelCol="1"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="17.5454545454545" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1257,14 +1254,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
